--- a/销售透视表_pandas.xlsx
+++ b/销售透视表_pandas.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="透视表结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>华南</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -453,6 +458,9 @@
       <c r="D2" t="n">
         <v>1250</v>
       </c>
+      <c r="E2" t="n">
+        <v>2700</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -468,6 +476,28 @@
       </c>
       <c r="D3" t="n">
         <v>2000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>48400</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>43400</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4450</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E4" t="n">
+        <v>51100</v>
       </c>
     </row>
   </sheetData>
